--- a/selenium_model/DEPLOYMENT_TEST_350_REPORT.xlsx
+++ b/selenium_model/DEPLOYMENT_TEST_350_REPORT.xlsx
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F304" t="n">
